--- a/src/data/output/apd_cargo_tria_combined_output.xlsx
+++ b/src/data/output/apd_cargo_tria_combined_output.xlsx
@@ -2,11 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -56,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -64,6 +67,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -468,18 +472,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I121"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="13.57142857142857" customWidth="1" min="1" max="1"/>
-    <col width="13.85714285714286" customWidth="1" min="2" max="2"/>
-    <col width="15.14285714285714" customWidth="1" min="3" max="3"/>
-    <col width="13.85714285714286" customWidth="1" min="4" max="4"/>
+    <col width="13.5546875" customWidth="1" min="1" max="1"/>
+    <col width="13.88671875" customWidth="1" min="2" max="2"/>
+    <col width="15.109375" customWidth="1" min="3" max="3"/>
+    <col width="13.88671875" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13.57142857142857" customWidth="1" min="6" max="6"/>
-    <col width="18.85714285714286" customWidth="1" min="7" max="7"/>
+    <col width="13.5546875" customWidth="1" min="6" max="6"/>
+    <col width="18.88671875" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="25.42857142857143" customWidth="1" min="9" max="9"/>
-    <col width="13.57142857142857" customWidth="1" min="10" max="24"/>
+    <col width="25.44140625" customWidth="1" min="9" max="9"/>
+    <col width="13.5546875" customWidth="1" min="10" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,27 +539,27 @@
           <t>TS-001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>0098665</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>58242.00</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>2135.00</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>1747.26</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>62124.26</t>
         </is>
@@ -567,11 +571,31 @@
           <t>TS-002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>0098826</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>20839.00</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>690.00</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>979.58</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>22508.58</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -579,11 +603,31 @@
           <t>TS-003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>0098836</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>6453.00</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>465.00</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>314.77</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>7232.77</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -591,11 +635,31 @@
           <t>TS-004</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>0098840</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>14837.00</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>670.00</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>445.11</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>15952.11</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -603,11 +667,31 @@
           <t>TS-005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>0098843</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>16950.00</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>880.00</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>401.18</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>18237.42</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -615,11 +699,31 @@
           <t>TS-006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>0098827</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>6754.00</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>475.00</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>162.66</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>7394.18</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -627,11 +731,31 @@
           <t>TS-007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>0098831</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>30677.00</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>1692.03</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>1533.85</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>33902.88</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -639,11 +763,31 @@
           <t>TS-008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>0098835</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>21198.00</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1515.00</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>454.26</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>23167.26</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -651,11 +795,31 @@
           <t>TS-009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>0098839</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>12162.00</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>440.00</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>573.40</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>13175.40</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -663,11 +827,31 @@
           <t>TS-010</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>0098911</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>14046.00</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1210.00</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>694.15</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>15950.15</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -675,11 +859,31 @@
           <t>TS-011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>0098832</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>5683.00</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>445.00</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>137.88</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>6268.02</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -687,11 +891,31 @@
           <t>TS-012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>0098833</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>4485.00</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>205.00</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>93.80</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>4783.80</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -699,11 +923,31 @@
           <t>TS-013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>0098838</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>9283.00</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>577.85</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>464.15</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>10325.00</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -711,11 +955,31 @@
           <t>TS-014</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>0098829</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>6168.00</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>770.00</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>185.04</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>7123.04</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -723,11 +987,31 @@
           <t>TS-015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>0098912</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>11573.00</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>234.46</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>11957.46</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -735,11 +1019,31 @@
           <t>TS-016</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="3" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>0098834</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>8460.00</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>570.00</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>410.87</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>9440.87</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -747,11 +1051,31 @@
           <t>TS-017</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>0098837</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>6284.00</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>340.00</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>188.52</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>6812.52</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -759,11 +1083,31 @@
           <t>TS-018</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
-      <c r="F19" s="3" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>0098841</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>9407.00</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>880.00</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>468.07</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>10755.07</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -771,11 +1115,31 @@
           <t>TS-019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>0098845</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>4155.00</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>230.00</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>124.65</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>4509.65</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -783,11 +1147,31 @@
           <t>TS-020</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>0098849</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>12527.00</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>972.58</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>626.35</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>14125.93</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -795,11 +1179,31 @@
           <t>TS-021</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>0098853</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>4827.00</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>264.48</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>241.35</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>5332.83</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -807,11 +1211,31 @@
           <t>TS-022</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>0098857</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>9954.00</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>599.86</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>497.70</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>11051.56</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -819,11 +1243,31 @@
           <t>TS-023</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="3" t="n"/>
-      <c r="F24" s="3" t="n"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>0098861</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>15680.00</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>165.00</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>470.40</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>16315.40</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -831,11 +1275,31 @@
           <t>TS-024</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="n"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>0098842</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>4548.00</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>373.64</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>227.40</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>5149.04</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -843,11 +1307,31 @@
           <t>TS-025</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>0098846</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>5945.00</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>395.00</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>288.47</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>6628.47</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -855,11 +1339,31 @@
           <t>TS-026</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>0098848</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>12377.00</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>902.13</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>618.85</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>13897.98</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -867,11 +1371,31 @@
           <t>TS-027</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>0098852</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>11084.00</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>290.00</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>332.52</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>11706.52</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -879,11 +1403,31 @@
           <t>TS-028</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>0098856</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>3605.00</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>280.00</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>176.77</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>4061.77</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -891,11 +1435,31 @@
           <t>TS-029</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>0098860</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>8723.00</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>790.00</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>285.39</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>9798.39</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -903,11 +1467,31 @@
           <t>TS-030</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>0098844</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>5809.00</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>275.00</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>174.27</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>6258.27</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -915,11 +1499,31 @@
           <t>TS-031</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>0098847</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>13031.00</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>1280.00</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>429.33</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>14740.33</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -927,11 +1531,31 @@
           <t>TS-032</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n"/>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>0098851</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>8238.00</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>167.26</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>8530.26</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -939,11 +1563,31 @@
           <t>TS-033</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n"/>
-      <c r="C34" s="3" t="n"/>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n"/>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>0098855</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>5172.00</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>545.52</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>258.60</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>5976.12</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -951,11 +1595,31 @@
           <t>TS-034</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
-      <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>0098859</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>9272.00</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>370.00</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>192.84</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>9834.84</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -963,11 +1627,31 @@
           <t>TS-035</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n"/>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="3" t="n"/>
-      <c r="E36" s="3" t="n"/>
-      <c r="F36" s="3" t="n"/>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>0098850</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>9443.00</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>538.33</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>472.15</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>10453.48</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -975,11 +1659,31 @@
           <t>TS-036</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n"/>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="n"/>
-      <c r="F37" s="3" t="n"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>0098854</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>5723.00</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>655.00</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>171.69</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>6549.69</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -987,11 +1691,31 @@
           <t>TS-037</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>0098858</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>6392.00</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>245.00</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>199.11</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>6836.11</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -999,11 +1723,31 @@
           <t>TS-038</t>
         </is>
       </c>
-      <c r="B39" s="3" t="n"/>
-      <c r="C39" s="3" t="n"/>
-      <c r="D39" s="3" t="n"/>
-      <c r="E39" s="3" t="n"/>
-      <c r="F39" s="3" t="n"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>0098862</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>6832.00</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>204.96</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>7536.96</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -1011,11 +1755,31 @@
           <t>TS-039</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="3" t="n"/>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>0098863</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>6914.00</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>515.00</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>222.87</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>7651.87</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -1023,11 +1787,31 @@
           <t>TS-040</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="3" t="n"/>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>0098867</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>4096.00</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>555.00</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>122.88</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>4773.88</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -1035,11 +1819,31 @@
           <t>TS-041</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="3" t="n"/>
-      <c r="E42" s="3" t="n"/>
-      <c r="F42" s="3" t="n"/>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>0098871</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>7069.00</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>475.00</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>150.88</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>7694.88</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -1047,11 +1851,31 @@
           <t>TS-042</t>
         </is>
       </c>
-      <c r="B43" s="3" t="n"/>
-      <c r="C43" s="3" t="n"/>
-      <c r="D43" s="3" t="n"/>
-      <c r="E43" s="3" t="n"/>
-      <c r="F43" s="3" t="n"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>0098877</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>7068.00</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>590.00</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>172.31</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>7832.99</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -1059,11 +1883,31 @@
           <t>TS-043</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>0098864</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>13718.00</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>715.00</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>432.99</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>14865.99</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -1071,11 +1915,31 @@
           <t>TS-044</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>0098868</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>6122.00</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>183.66</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>6805.66</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -1083,11 +1947,31 @@
           <t>TS-045</t>
         </is>
       </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
-      <c r="F46" s="3" t="n"/>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>0098872</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>4492.00</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>134.76</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>4876.76</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -1095,11 +1979,31 @@
           <t>TS-046</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="3" t="n"/>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="3" t="n"/>
-      <c r="F47" s="3" t="n"/>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>0098865</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>8161.00</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>800.00</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>268.83</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>9229.83</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -1107,11 +2011,31 @@
           <t>TS-047</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
-      <c r="E48" s="3" t="n"/>
-      <c r="F48" s="3" t="n"/>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>0098869</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>18209.00</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>650.00</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>858.09</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>19717.09</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -1119,11 +2043,31 @@
           <t>TS-048</t>
         </is>
       </c>
-      <c r="B49" s="3" t="n"/>
-      <c r="C49" s="3" t="n"/>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>0098874</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>8876.00</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>900.00</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>266.28</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>10042.28</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -1131,11 +2075,31 @@
           <t>TS-049</t>
         </is>
       </c>
-      <c r="B50" s="3" t="n"/>
-      <c r="C50" s="3" t="n"/>
-      <c r="D50" s="3" t="n"/>
-      <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n"/>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>0098866</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>5363.00</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>250.00</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>255.39</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>5868.39</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -1143,11 +2107,31 @@
           <t>TS-050</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="3" t="n"/>
-      <c r="E51" s="3" t="n"/>
-      <c r="F51" s="3" t="n"/>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>0098870</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>18139.00</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>1269.73</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>544.17</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>19952.90</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -1155,11 +2139,31 @@
           <t>TS-051</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n"/>
-      <c r="C52" s="3" t="n"/>
-      <c r="D52" s="3" t="n"/>
-      <c r="E52" s="3" t="n"/>
-      <c r="F52" s="3" t="n"/>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>0098913</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>18953.00</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>181.86</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>947.65</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>20082.51</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -1167,11 +2171,31 @@
           <t>TS-052</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n"/>
-      <c r="C53" s="3" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n"/>
-      <c r="F53" s="3" t="n"/>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>0098879</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>4856.00</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>485.00</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>160.23</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>5501.23</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -1179,11 +2203,31 @@
           <t>TS-053</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n"/>
-      <c r="C54" s="3" t="n"/>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n"/>
-      <c r="F54" s="3" t="n"/>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>0098882</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>7008.00</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>436.02</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>350.40</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>7794.42</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -1191,11 +2235,31 @@
           <t>TS-054</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n"/>
-      <c r="C55" s="3" t="n"/>
-      <c r="D55" s="3" t="n"/>
-      <c r="E55" s="3" t="n"/>
-      <c r="F55" s="3" t="n"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>0098878</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>5801.00</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>505.00</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>141.89</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>6450.09</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -1203,11 +2267,31 @@
           <t>TS-055</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n"/>
-      <c r="C56" s="3" t="n"/>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="3" t="n"/>
-      <c r="F56" s="3" t="n"/>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>0098908</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>10264.00</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>1015.79</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>513.20</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>11792.99</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -1215,11 +2299,31 @@
           <t>TS-056</t>
         </is>
       </c>
-      <c r="B57" s="3" t="n"/>
-      <c r="C57" s="3" t="n"/>
-      <c r="D57" s="3" t="n"/>
-      <c r="E57" s="3" t="n"/>
-      <c r="F57" s="3" t="n"/>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>0098876</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>9947.00</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>275.00</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>204.44</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>10426.44</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -1227,11 +2331,31 @@
           <t>TS-057</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n"/>
-      <c r="C58" s="3" t="n"/>
-      <c r="D58" s="3" t="n"/>
-      <c r="E58" s="3" t="n"/>
-      <c r="F58" s="3" t="n"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>0098881</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>7789.00</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>545.00</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>379.20</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>8713.20</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -1239,11 +2363,31 @@
           <t>TS-058</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n"/>
-      <c r="C59" s="3" t="n"/>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="3" t="n"/>
-      <c r="F59" s="3" t="n"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>0098880</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>8055.00</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>894.17</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>402.75</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>9351.92</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -1251,11 +2395,31 @@
           <t>TS-059</t>
         </is>
       </c>
-      <c r="B60" s="3" t="n"/>
-      <c r="C60" s="3" t="n"/>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="3" t="n"/>
-      <c r="F60" s="3" t="n"/>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>0098884</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>14568.00</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>203.70</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>728.40</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>15500.10</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -1263,11 +2427,31 @@
           <t>TS-060</t>
         </is>
       </c>
-      <c r="B61" s="3" t="n"/>
-      <c r="C61" s="3" t="n"/>
-      <c r="D61" s="3" t="n"/>
-      <c r="E61" s="3" t="n"/>
-      <c r="F61" s="3" t="n"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>0098885</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>5895.00</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>335.00</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>176.85</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>6406.85</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -1275,11 +2459,31 @@
           <t>TS-061</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n"/>
-      <c r="C62" s="3" t="n"/>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="3" t="n"/>
-      <c r="F62" s="3" t="n"/>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>0098886</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>10597.00</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>430.00</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>501.74</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>11528.74</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -1287,11 +2491,31 @@
           <t>TS-062</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n"/>
-      <c r="C63" s="3" t="n"/>
-      <c r="D63" s="3" t="n"/>
-      <c r="E63" s="3" t="n"/>
-      <c r="F63" s="3" t="n"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>0098887</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>10523.00</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>666.57</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>526.15</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>11715.72</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -1299,11 +2523,31 @@
           <t>TS-063</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n"/>
-      <c r="C64" s="3" t="n"/>
-      <c r="D64" s="3" t="n"/>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>0098888</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>14267.00</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>235.00</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>659.85</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>15161.85</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -1311,11 +2555,31 @@
           <t>TS-064</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
-      <c r="F65" s="3" t="n"/>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>0098889</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>7560.00</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>575.00</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>370.15</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>8505.15</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -1323,11 +2587,31 @@
           <t>TS-065</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>0098890</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>5552.00</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>500.00</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>166.56</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>6218.56</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -1335,11 +2619,31 @@
           <t>TS-066</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
-      <c r="F67" s="3" t="n"/>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>0098891</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>8512.00</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>405.00</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>200.63</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>9120.75</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -1347,11 +2651,31 @@
           <t>TS-067</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>0098910</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>9271.00</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>167.81</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>463.55</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>9902.36</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -1359,11 +2683,31 @@
           <t>TS-068</t>
         </is>
       </c>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>0098893</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>6536.00</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>740.00</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>196.08</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>7472.08</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -1371,11 +2715,31 @@
           <t>TS-069</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
-      <c r="F70" s="3" t="n"/>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>0098894</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>3818.00</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>366.45</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>190.90</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>4375.35</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -1383,11 +2747,31 @@
           <t>TS-070</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>0098895</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>14513.00</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>375.00</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>446.64</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>15334.64</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -1395,11 +2779,31 @@
           <t>TS-071</t>
         </is>
       </c>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>0098897</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>4498.00</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>445.00</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>224.91</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>5167.91</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -1407,11 +2811,31 @@
           <t>TS-072</t>
         </is>
       </c>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>0098896</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>6736.00</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>825.21</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>336.80</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>7898.01</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -1419,11 +2843,31 @@
           <t>TS-073</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
-      <c r="F74" s="3" t="n"/>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>0098898</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>11578.00</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>320.00</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>356.94</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>12254.94</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -1431,11 +2875,31 @@
           <t>TS-074</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
-      <c r="F75" s="3" t="n"/>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>0098899</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>6320.00</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>340.00</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>149.85</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>6812.18</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -1443,11 +2907,31 @@
           <t>TS-075</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>0098909</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>6168.00</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>640.00</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>204.24</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>7012.24</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -1455,11 +2939,31 @@
           <t>TS-076</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>0098900</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>7134.00</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>219.27</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>7528.27</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -1467,11 +2971,31 @@
           <t>TS-077</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
-      <c r="F78" s="3" t="n"/>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>0098902</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>10225.00</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>830.00</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>248.75</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>11307.62</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -1479,11 +3003,31 @@
           <t>TS-078</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
-      <c r="F79" s="3" t="n"/>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>0098903</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>6692.00</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>770.00</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>167.90</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>7632.51</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -1491,11 +3035,31 @@
           <t>TS-079</t>
         </is>
       </c>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="n"/>
-      <c r="F80" s="3" t="n"/>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>0098904</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>6869.00</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>275.00</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>206.07</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>7350.07</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -1503,329 +3067,349 @@
           <t>TS-080</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>0098905</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>10134.00</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>475.00</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>238.70</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>10851.41</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="2" t="n"/>
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2" t="n"/>
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="2" t="n"/>
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="n"/>
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2" t="n"/>
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2" t="n"/>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n"/>
+      <c r="B86" s="4" t="n"/>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2" t="n"/>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2" t="n"/>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2" t="n"/>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="2" t="n"/>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
-      <c r="F90" s="3" t="n"/>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="2" t="n"/>
-      <c r="B91" s="3" t="n"/>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="n"/>
-      <c r="F91" s="3" t="n"/>
+      <c r="B91" s="4" t="n"/>
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="n"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="2" t="n"/>
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="n"/>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="2" t="n"/>
-      <c r="B93" s="3" t="n"/>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="2" t="n"/>
-      <c r="B94" s="3" t="n"/>
-      <c r="C94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="2" t="n"/>
-      <c r="B95" s="3" t="n"/>
-      <c r="C95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="n"/>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="2" t="n"/>
-      <c r="B96" s="3" t="n"/>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="n"/>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="2" t="n"/>
-      <c r="B97" s="3" t="n"/>
-      <c r="C97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="n"/>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="2" t="n"/>
-      <c r="B98" s="3" t="n"/>
-      <c r="C98" s="3" t="n"/>
-      <c r="D98" s="3" t="n"/>
-      <c r="E98" s="3" t="n"/>
-      <c r="F98" s="3" t="n"/>
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="2" t="n"/>
-      <c r="B99" s="3" t="n"/>
-      <c r="C99" s="3" t="n"/>
-      <c r="D99" s="3" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n"/>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="2" t="n"/>
-      <c r="B100" s="3" t="n"/>
-      <c r="C100" s="3" t="n"/>
-      <c r="D100" s="3" t="n"/>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="3" t="n"/>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="2" t="n"/>
-      <c r="B101" s="3" t="n"/>
-      <c r="C101" s="3" t="n"/>
-      <c r="D101" s="3" t="n"/>
-      <c r="E101" s="3" t="n"/>
-      <c r="F101" s="3" t="n"/>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2" t="n"/>
-      <c r="B102" s="3" t="n"/>
-      <c r="C102" s="3" t="n"/>
-      <c r="D102" s="3" t="n"/>
-      <c r="E102" s="3" t="n"/>
-      <c r="F102" s="3" t="n"/>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="2" t="n"/>
-      <c r="B103" s="3" t="n"/>
-      <c r="C103" s="3" t="n"/>
-      <c r="D103" s="3" t="n"/>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n"/>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="2" t="n"/>
-      <c r="B104" s="3" t="n"/>
-      <c r="C104" s="3" t="n"/>
-      <c r="D104" s="3" t="n"/>
-      <c r="E104" s="3" t="n"/>
-      <c r="F104" s="3" t="n"/>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="2" t="n"/>
-      <c r="B105" s="3" t="n"/>
-      <c r="C105" s="3" t="n"/>
-      <c r="D105" s="3" t="n"/>
-      <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n"/>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="2" t="n"/>
-      <c r="B106" s="3" t="n"/>
-      <c r="C106" s="3" t="n"/>
-      <c r="D106" s="3" t="n"/>
-      <c r="E106" s="3" t="n"/>
-      <c r="F106" s="3" t="n"/>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="2" t="n"/>
-      <c r="B107" s="3" t="n"/>
-      <c r="C107" s="3" t="n"/>
-      <c r="D107" s="3" t="n"/>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n"/>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="2" t="n"/>
-      <c r="B108" s="3" t="n"/>
-      <c r="C108" s="3" t="n"/>
-      <c r="D108" s="3" t="n"/>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n"/>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="2" t="n"/>
-      <c r="B109" s="3" t="n"/>
-      <c r="C109" s="3" t="n"/>
-      <c r="D109" s="3" t="n"/>
-      <c r="E109" s="3" t="n"/>
-      <c r="F109" s="3" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="2" t="n"/>
-      <c r="B110" s="3" t="n"/>
-      <c r="C110" s="3" t="n"/>
-      <c r="D110" s="3" t="n"/>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="3" t="n"/>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="n"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2" t="n"/>
-      <c r="B111" s="3" t="n"/>
-      <c r="C111" s="3" t="n"/>
-      <c r="D111" s="3" t="n"/>
-      <c r="E111" s="3" t="n"/>
-      <c r="F111" s="3" t="n"/>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2" t="n"/>
-      <c r="B112" s="3" t="n"/>
-      <c r="C112" s="3" t="n"/>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2" t="n"/>
-      <c r="B113" s="3" t="n"/>
-      <c r="C113" s="3" t="n"/>
-      <c r="D113" s="3" t="n"/>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="n"/>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2" t="n"/>
-      <c r="B114" s="3" t="n"/>
-      <c r="C114" s="3" t="n"/>
-      <c r="D114" s="3" t="n"/>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n"/>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2" t="n"/>
-      <c r="B115" s="3" t="n"/>
-      <c r="C115" s="3" t="n"/>
-      <c r="D115" s="3" t="n"/>
-      <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2" t="n"/>
-      <c r="B116" s="3" t="n"/>
-      <c r="C116" s="3" t="n"/>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n"/>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2" t="n"/>
-      <c r="B117" s="3" t="n"/>
-      <c r="C117" s="3" t="n"/>
-      <c r="D117" s="3" t="n"/>
-      <c r="E117" s="3" t="n"/>
-      <c r="F117" s="3" t="n"/>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2" t="n"/>
-      <c r="B118" s="3" t="n"/>
-      <c r="C118" s="3" t="n"/>
-      <c r="D118" s="3" t="n"/>
-      <c r="E118" s="3" t="n"/>
-      <c r="F118" s="3" t="n"/>
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="2" t="n"/>
-      <c r="B119" s="3" t="n"/>
-      <c r="C119" s="3" t="n"/>
-      <c r="D119" s="3" t="n"/>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n"/>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2" t="n"/>
-      <c r="B120" s="3" t="n"/>
-      <c r="C120" s="3" t="n"/>
-      <c r="D120" s="3" t="n"/>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>